--- a/partner_results/dik/ClassMissingEnglishDefinition_dik.xlsx
+++ b/partner_results/dik/ClassMissingEnglishDefinition_dik.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,11 +434,6 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Definition</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
           <t>Add English definition</t>
         </is>
       </c>
@@ -446,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>mixing chamber temperature control unit [dik]</t>
+          <t>electrical power [dik]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>extensive quality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -460,17 +455,16 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tetrabenzylthiuramdisulfide [dik]</t>
+          <t>haul-off speed [dik]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -479,17 +473,16 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>product data sheet [dik]</t>
+          <t>tetrabenzylthiuramdisulfide [dik]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -498,17 +491,16 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>rotor speed [dik]</t>
+          <t>torque unit [dik]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>measurement unit label</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -517,17 +509,16 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>quality of a liquid [dik]</t>
+          <t>safety data sheet [dik]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -536,17 +527,16 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>die geometry [dik]</t>
+          <t>Newtonmeter [dik]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>geometry [imr]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -555,17 +545,16 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dithiocarbamate [dik]</t>
+          <t>ethylidene norbornene [dik]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dithiocarbamate anions</t>
+          <t>chemical substance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -574,17 +563,16 @@
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>drop door temperature [dik]</t>
+          <t>screw speed [dik]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -593,17 +581,16 @@
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organodiyl group [dik]</t>
+          <t>setting roll speed [dik]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>organic divalent group [chebi]</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -612,17 +599,16 @@
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rotor temperature control unit [dik]</t>
+          <t>quality of a solid [dik]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -631,17 +617,16 @@
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>screw speed [dik]</t>
+          <t>optical quality [dik]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -650,17 +635,16 @@
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pin zone temperature [dik]</t>
+          <t>time of addition [dik]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>temporal interval</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -669,17 +653,16 @@
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>material processing [dik]</t>
+          <t>drop door [dik]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -688,17 +671,16 @@
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>extrudate cross section [dik]</t>
+          <t>setting roll temperature [dik]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>fiat object part</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -707,12 +689,11 @@
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>setting roll [dik]</t>
+          <t>setting roll temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -726,17 +707,16 @@
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>number of mixing stages [dik]</t>
+          <t>rotor temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -745,12 +725,11 @@
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>viscometer [dik]</t>
+          <t>rotor [dik]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -764,17 +743,16 @@
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>setting point [dik]</t>
+          <t>stamp temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -783,36 +761,30 @@
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>single screw extruder [dik]</t>
+          <t>physical quality [dik]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>extruder</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
+          <t>quality</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hydrocarbylene group [dik]</t>
+          <t>fixed roll temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -821,17 +793,16 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>torque unit [dik]</t>
+          <t>Mooney shearing-disc viscometer [dik]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>measurement unit label</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -840,17 +811,16 @@
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>safety data sheet [dik]</t>
+          <t>hydrocarbylene group [dik]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>organodiyl group [chebi]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -859,17 +829,16 @@
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vulcanization time [dik]</t>
+          <t>pin zone temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>temporal interval</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -878,17 +847,16 @@
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>specific surface [dik]</t>
+          <t>number of mixing stages [dik]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -897,17 +865,16 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Newtonmeter [dik]</t>
+          <t>organic divalent group [dik]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>organic group [chebi]</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -916,17 +883,16 @@
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>molding zone temperature control unit [dik]</t>
+          <t>vulcanization time [dik]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>temporal interval</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -935,17 +901,16 @@
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>screw temperature [dik]</t>
+          <t>melting range [dik]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -954,17 +919,16 @@
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mooney unit [dik]</t>
+          <t>torque [dik]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>measurement unit label</t>
+          <t>extensive quality</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -973,17 +937,16 @@
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fixed roll temperature [dik]</t>
+          <t>rotor torque [dik]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -992,17 +955,16 @@
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stamp distance [dik]</t>
+          <t>setting roll [dik]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1011,17 +973,16 @@
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>feeding zone temperature [dik]</t>
+          <t>quality of a substance [dik]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1030,17 +991,16 @@
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>volume-specific surface [dik]</t>
+          <t>temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1049,36 +1009,30 @@
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>fixed roll [dik]</t>
+          <t>ethylidene group [dik]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>device</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
+          <t>organodiyl group [chebi]</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>mixing [dik]</t>
+          <t>fixed roll [dik]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1087,12 +1041,11 @@
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>engine [dik]</t>
+          <t>feeding roll temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1106,17 +1059,16 @@
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>torque [dik]</t>
+          <t>pin extruder [dik]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>extensive quality</t>
+          <t>extruder</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1125,36 +1077,30 @@
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>rotor temperature [dik]</t>
+          <t>function [dik]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>device specification</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
+          <t>function</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>oil content [dik]</t>
+          <t>mixing chamber [dik]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1163,17 +1109,16 @@
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>conveyor belt [dik]</t>
+          <t>setting point [dik]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1182,17 +1127,16 @@
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>setting roll temperature control unit [dik]</t>
+          <t>die geometry [dik]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>geometry [imr]</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1201,47 +1145,52 @@
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>function [dik]</t>
+          <t>di(benzothiazol-2-yl)disulfide [dik]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>function</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>organic disulfide</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ethylidene group [dik]</t>
+          <t>extrudate cross section [dik]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>organodiyl group [chebi]</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>fiat object part</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>melting range [dik]</t>
+          <t>mixing [dik]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1250,32 +1199,34 @@
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>physical quality [dik]</t>
+          <t>organodiyl group [dik]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>quality</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>organic divalent group [chebi]</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>electrical power [dik]</t>
+          <t>viscometer [dik]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>extensive quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1284,36 +1235,30 @@
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Pressure Sensor [dik]</t>
+          <t>zinc oxide [dik]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>sensor [chmo]</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Alexander Aschemann</t>
-        </is>
-      </c>
+          <t>chemical substance</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>organic divalent group [dik]</t>
+          <t>feeding zone temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>organic group [chebi]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1322,17 +1267,16 @@
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>zinc dibenzyldithiocarbamate [dik]</t>
+          <t>mixing chamber temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>vulcanisation accelerator [dik]</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1341,12 +1285,11 @@
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>surface defect [dik]</t>
+          <t>drop door temperature [dik]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1360,17 +1303,16 @@
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>mixing chamber temperature [dik]</t>
+          <t>temperature sensor [dik]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>sensor [chmo]</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1379,17 +1321,16 @@
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>quality of a solid [dik]</t>
+          <t>screw temperature [dik]</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1398,17 +1339,16 @@
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>mixing chamber [dik]</t>
+          <t>quality of a liquid [dik]</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>quality</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1417,17 +1357,16 @@
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>quality of a substance [dik]</t>
+          <t>temperature measuring sword [dik]</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>quality</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1436,17 +1375,16 @@
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>group [dik]</t>
+          <t>fixed roll temperature [dik]</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>chemical entity</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1455,12 +1393,11 @@
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>fixed roll temperature control unit [dik]</t>
+          <t>feeding roll [dik]</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1474,12 +1411,11 @@
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>screw temperature control unit [dik]</t>
+          <t>curemeter [dik]</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1493,12 +1429,11 @@
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>stamp temperature [dik]</t>
+          <t>mixing chamber temperature [dik]</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1512,17 +1447,16 @@
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>setting roll temperature [dik]</t>
+          <t>material processing [dik]</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>process</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1531,17 +1465,16 @@
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mooney shearing-disc viscometer [dik]</t>
+          <t>concentration [dik]</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1550,17 +1483,16 @@
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>feeding roll temperature control unit [dik]</t>
+          <t>surface [dik]</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>surface layer (fiat object part)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1569,17 +1501,16 @@
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>temperature measuring sword [dik]</t>
+          <t>product data sheet [dik]</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1588,17 +1519,16 @@
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>setting roll speed [dik]</t>
+          <t>conveyor belt [dik]</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1607,17 +1537,16 @@
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>pin extruder [dik]</t>
+          <t>mixing time [dik]</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>extruder</t>
+          <t>temporal interval</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1626,17 +1555,16 @@
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>processed material [dik]</t>
+          <t>surface defect [dik]</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1645,17 +1573,16 @@
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>manufacturing specification [dik]</t>
+          <t>zinc dibenzyldithiocarbamate [dik]</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>vulcanisation accelerator [dik]</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1664,17 +1591,16 @@
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>temperature sensor [dik]</t>
+          <t>single screw extruder [dik]</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sensor [chmo]</t>
+          <t>extruder</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1683,17 +1609,16 @@
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>organic group [dik]</t>
+          <t>rotor temperature [dik]</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>group [chebi]</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1702,12 +1627,11 @@
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>curemeter [dik]</t>
+          <t>engine [dik]</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1721,17 +1645,16 @@
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>gearbox [dik]</t>
+          <t>rotor speed [dik]</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>device specification</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1740,17 +1663,16 @@
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>surface [dik]</t>
+          <t>manufacturing specification [dik]</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>surface layer (fiat object part)</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1759,17 +1681,16 @@
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>optical quality [dik]</t>
+          <t>organic group [dik]</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>group [chebi]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1778,17 +1699,16 @@
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>mixing time [dik]</t>
+          <t>oil content [dik]</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>temporal interval</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1797,17 +1717,16 @@
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>rotor [dik]</t>
+          <t>dithiocarbamate [dik]</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>dithiocarbamate anions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1816,12 +1735,11 @@
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>molding zone temperature [dik]</t>
+          <t>feeding zone temperature [dik]</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1835,12 +1753,11 @@
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>feeding roll temperature [dik]</t>
+          <t>pin zone temperature [dik]</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1854,17 +1771,16 @@
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>stamp temperature control unit [dik]</t>
+          <t>stamp temperature [dik]</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1873,17 +1789,16 @@
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>rotor torque [dik]</t>
+          <t>feeding roll temperature [dik]</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>device specification</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1892,12 +1807,11 @@
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>feeding roll [dik]</t>
+          <t>screw temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1911,17 +1825,16 @@
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ethylidene norbornene [dik]</t>
+          <t>processed material [dik]</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>chemical substance</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1930,17 +1843,16 @@
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>pin zone temperature control unit [dik]</t>
+          <t>fixed roll speed [dik]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1949,17 +1861,16 @@
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>time of addition [dik]</t>
+          <t>group [dik]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>temporal interval</t>
+          <t>chemical entity</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1968,32 +1879,34 @@
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>zinc oxide [dik]</t>
+          <t>molding zone temperature control unit [dik]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>chemical substance</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>device</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Alexander Aschemann</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>concentration [dik]</t>
+          <t>specific surface [dik]</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>surface [dik]</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2002,17 +1915,16 @@
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>surface temperature [dik]</t>
+          <t>Mooney unit [dik]</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>measurement unit label</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2021,17 +1933,16 @@
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ethylene group [dik]</t>
+          <t>stamp distance [dik]</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>hydrocarbylene group [chebi]</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2040,17 +1951,16 @@
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>di(benzothiazol-2-yl)disulfide [dik]</t>
+          <t>Pressure Sensor [dik]</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>organic disulfide</t>
+          <t>sensor [chmo]</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2059,17 +1969,16 @@
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>thiuram [dik]</t>
+          <t>molding zone temperature [dik]</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>vulcanisation accelerator [dik]</t>
+          <t>intensive quality</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2078,17 +1987,16 @@
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>haul-off speed [dik]</t>
+          <t>volume-specific surface [dik]</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>intensive quality</t>
+          <t>surface [dik]</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2097,12 +2005,11 @@
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>drop door [dik]</t>
+          <t>gearbox [dik]</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2116,17 +2023,16 @@
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>feeding zone temperature control unit [dik]</t>
+          <t>ethylene group [dik]</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>hydrocarbylene group [chebi]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2135,17 +2041,16 @@
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>temperature control unit [dik]</t>
+          <t>thiuram [dik]</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>vulcanisation accelerator [dik]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2154,12 +2059,11 @@
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>fixed roll speed [dik]</t>
+          <t>surface temperature [dik]</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2173,7 +2077,6 @@
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
